--- a/build/temp/pages/ValueSet-cibmtr-cs-vitalsigns.xlsx
+++ b/build/temp/pages/ValueSet-cibmtr-cs-vitalsigns.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.10</t>
+    <t>0.1.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -59,19 +59,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T10:10:52-05:00</t>
+    <t>2026-08-27T20:01:54-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program (http://www.cibmtr.org)</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP (http://www.cibmtr.org)</t>
   </si>
   <si>
     <t>Bob Milius (bmilius@nmdp.org)</t>
